--- a/docs/BlueFox_CUO_v2_Production.xlsx
+++ b/docs/BlueFox_CUO_v2_Production.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\Minijeu Yllias\V3_BlueFox odyssey Fondation IA\V3_EXECUTABL_fondation IA\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77DF406-7066-4CAC-9CA3-75A2870F53F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F006CD3-E639-43FC-9AC2-FDAD6F784217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3210" yWindow="2340" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
